--- a/19/ML/Projects/Regression/CorporateSalary.xlsx
+++ b/19/ML/Projects/Regression/CorporateSalary.xlsx
@@ -5,16 +5,20 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVRAJ SHINDE\JupiterWorking\Projects\Regression\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Study\Eathans\Ethans\19\ML\Projects\Regression\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <pivotCaches>
+    <pivotCache cacheId="7" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="31">
   <si>
     <t>Designation</t>
   </si>
@@ -91,6 +95,33 @@
   <si>
     <t>Sales</t>
   </si>
+  <si>
+    <t>Dependant Column</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>x3</t>
+  </si>
+  <si>
+    <t>x4</t>
+  </si>
+  <si>
+    <t>x5</t>
+  </si>
+  <si>
+    <t>x6</t>
+  </si>
+  <si>
+    <t>Independent Column</t>
+  </si>
 </sst>
 </file>
 
@@ -130,7 +161,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -138,16 +169,142 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -164,6 +321,1262 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="SHIVRAJ SHINDE" refreshedDate="46227.369496064814" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="100">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A5:G105" sheet="Sheet2"/>
+  </cacheSource>
+  <cacheFields count="7">
+    <cacheField name="Designation" numFmtId="0">
+      <sharedItems count="6">
+        <s v="Senior Analyst"/>
+        <s v="Director"/>
+        <s v="Manager"/>
+        <s v="Lead Consultant"/>
+        <s v="Junior Analyst"/>
+        <s v="Senior Manager"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Education" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Bachelor's"/>
+        <s v="Master's"/>
+        <s v="PhD"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Department" numFmtId="0">
+      <sharedItems count="6">
+        <s v="Data Science"/>
+        <s v="Marketing"/>
+        <s v="Engineering"/>
+        <s v="HR"/>
+        <s v="Product"/>
+        <s v="Sales"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="TenureYears" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.6" maxValue="11.8" count="69">
+        <n v="8.6999999999999993"/>
+        <n v="6.9"/>
+        <n v="3.9"/>
+        <n v="5.3"/>
+        <n v="3.4"/>
+        <n v="7.5"/>
+        <n v="1.4"/>
+        <n v="0.6"/>
+        <n v="7.7"/>
+        <n v="2.7"/>
+        <n v="1.3"/>
+        <n v="5.0999999999999996"/>
+        <n v="1.1000000000000001"/>
+        <n v="10.7"/>
+        <n v="0.8"/>
+        <n v="7.2"/>
+        <n v="5.5"/>
+        <n v="8.1999999999999993"/>
+        <n v="4.3"/>
+        <n v="2.2999999999999998"/>
+        <n v="11.8"/>
+        <n v="10.1"/>
+        <n v="10.4"/>
+        <n v="0.9"/>
+        <n v="4"/>
+        <n v="6.7"/>
+        <n v="10"/>
+        <n v="3.6"/>
+        <n v="11.6"/>
+        <n v="5.8"/>
+        <n v="10.199999999999999"/>
+        <n v="5.2"/>
+        <n v="8.5"/>
+        <n v="2.1"/>
+        <n v="2"/>
+        <n v="1"/>
+        <n v="9.1"/>
+        <n v="2.6"/>
+        <n v="5.4"/>
+        <n v="8.4"/>
+        <n v="1.2"/>
+        <n v="11"/>
+        <n v="5.6"/>
+        <n v="3.3"/>
+        <n v="1.6"/>
+        <n v="11.2"/>
+        <n v="7.8"/>
+        <n v="6.4"/>
+        <n v="8.1"/>
+        <n v="8.9"/>
+        <n v="7"/>
+        <n v="1.9"/>
+        <n v="4.4000000000000004"/>
+        <n v="4.0999999999999996"/>
+        <n v="2.5"/>
+        <n v="0.7"/>
+        <n v="9.3000000000000007"/>
+        <n v="9.8000000000000007"/>
+        <n v="4.5"/>
+        <n v="8"/>
+        <n v="11.4"/>
+        <n v="3.5"/>
+        <n v="6.3"/>
+        <n v="7.6"/>
+        <n v="10.5"/>
+        <n v="9.6999999999999993"/>
+        <n v="8.3000000000000007"/>
+        <n v="7.1"/>
+        <n v="9.9"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="ProjectsCompleted" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="24" count="22">
+        <n v="12"/>
+        <n v="13"/>
+        <n v="14"/>
+        <n v="15"/>
+        <n v="3"/>
+        <n v="20"/>
+        <n v="19"/>
+        <n v="4"/>
+        <n v="24"/>
+        <n v="18"/>
+        <n v="9"/>
+        <n v="11"/>
+        <n v="10"/>
+        <n v="8"/>
+        <n v="5"/>
+        <n v="22"/>
+        <n v="6"/>
+        <n v="17"/>
+        <n v="21"/>
+        <n v="23"/>
+        <n v="16"/>
+        <n v="7"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="PerformanceScore" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.5" maxValue="5" count="26">
+        <n v="4.5999999999999996"/>
+        <n v="4.3"/>
+        <n v="2.7"/>
+        <n v="5"/>
+        <n v="3.4"/>
+        <n v="4.5"/>
+        <n v="4.9000000000000004"/>
+        <n v="4.4000000000000004"/>
+        <n v="3.9"/>
+        <n v="3.6"/>
+        <n v="4.8"/>
+        <n v="2.8"/>
+        <n v="3.7"/>
+        <n v="2.5"/>
+        <n v="2.6"/>
+        <n v="4.0999999999999996"/>
+        <n v="4"/>
+        <n v="3.2"/>
+        <n v="4.7"/>
+        <n v="3.1"/>
+        <n v="3.8"/>
+        <n v="4.2"/>
+        <n v="3"/>
+        <n v="3.3"/>
+        <n v="2.9"/>
+        <n v="3.5"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Salary" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="65600" maxValue="239300"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="100">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="119300"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="212200"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="139400"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="137200"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="90100"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="4"/>
+    <x v="4"/>
+    <n v="93100"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="4"/>
+    <n v="65600"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="6"/>
+    <x v="5"/>
+    <n v="162400"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="8"/>
+    <x v="7"/>
+    <x v="6"/>
+    <n v="118500"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="9"/>
+    <x v="8"/>
+    <x v="3"/>
+    <n v="152800"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="9"/>
+    <x v="7"/>
+    <n v="71300"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="10"/>
+    <x v="4"/>
+    <n v="212200"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="12"/>
+    <x v="11"/>
+    <x v="2"/>
+    <n v="146000"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="13"/>
+    <x v="4"/>
+    <x v="7"/>
+    <n v="100400"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="14"/>
+    <x v="5"/>
+    <x v="8"/>
+    <n v="76900"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="15"/>
+    <x v="12"/>
+    <x v="9"/>
+    <n v="98500"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="16"/>
+    <x v="13"/>
+    <x v="10"/>
+    <n v="106300"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="17"/>
+    <x v="14"/>
+    <x v="11"/>
+    <n v="115100"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="18"/>
+    <x v="15"/>
+    <x v="12"/>
+    <n v="117100"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="19"/>
+    <x v="6"/>
+    <x v="13"/>
+    <n v="107000"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="20"/>
+    <x v="2"/>
+    <x v="12"/>
+    <n v="151000"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="21"/>
+    <x v="0"/>
+    <x v="14"/>
+    <n v="113800"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="22"/>
+    <x v="14"/>
+    <x v="11"/>
+    <n v="110600"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="15"/>
+    <x v="11"/>
+    <n v="111000"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="14"/>
+    <x v="15"/>
+    <n v="94700"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="11"/>
+    <x v="7"/>
+    <n v="131000"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="25"/>
+    <x v="16"/>
+    <x v="16"/>
+    <n v="93200"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="12"/>
+    <x v="6"/>
+    <n v="139200"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="26"/>
+    <x v="7"/>
+    <x v="4"/>
+    <n v="122800"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="27"/>
+    <x v="9"/>
+    <x v="17"/>
+    <n v="95100"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="28"/>
+    <x v="7"/>
+    <x v="18"/>
+    <n v="142400"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="29"/>
+    <x v="17"/>
+    <x v="19"/>
+    <n v="92900"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="30"/>
+    <x v="14"/>
+    <x v="6"/>
+    <n v="87800"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="6"/>
+    <x v="13"/>
+    <n v="157800"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="31"/>
+    <x v="9"/>
+    <x v="6"/>
+    <n v="218200"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="32"/>
+    <x v="13"/>
+    <x v="14"/>
+    <n v="134100"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="33"/>
+    <x v="8"/>
+    <x v="18"/>
+    <n v="101600"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="34"/>
+    <x v="16"/>
+    <x v="20"/>
+    <n v="71400"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="134700"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="2"/>
+    <n v="115300"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="35"/>
+    <x v="8"/>
+    <x v="8"/>
+    <n v="94100"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="2"/>
+    <x v="6"/>
+    <n v="99400"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="16"/>
+    <x v="8"/>
+    <x v="20"/>
+    <n v="78100"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="36"/>
+    <x v="7"/>
+    <x v="15"/>
+    <n v="168900"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="12"/>
+    <x v="21"/>
+    <n v="93400"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="37"/>
+    <x v="9"/>
+    <x v="9"/>
+    <n v="115100"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="9"/>
+    <x v="15"/>
+    <n v="109800"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="38"/>
+    <x v="18"/>
+    <x v="16"/>
+    <n v="126400"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="39"/>
+    <x v="17"/>
+    <x v="10"/>
+    <n v="138200"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="40"/>
+    <x v="19"/>
+    <x v="14"/>
+    <n v="81700"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="41"/>
+    <x v="2"/>
+    <x v="17"/>
+    <n v="239300"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="42"/>
+    <x v="5"/>
+    <x v="6"/>
+    <n v="149700"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="43"/>
+    <x v="9"/>
+    <x v="18"/>
+    <n v="171800"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="44"/>
+    <x v="14"/>
+    <x v="9"/>
+    <n v="155300"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="37"/>
+    <x v="1"/>
+    <x v="15"/>
+    <n v="126300"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="45"/>
+    <x v="12"/>
+    <x v="17"/>
+    <n v="182800"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="46"/>
+    <x v="5"/>
+    <x v="22"/>
+    <n v="93300"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="47"/>
+    <x v="1"/>
+    <x v="12"/>
+    <n v="98000"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="48"/>
+    <x v="12"/>
+    <x v="4"/>
+    <n v="93100"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="13"/>
+    <x v="16"/>
+    <n v="119200"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="49"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="119900"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="35"/>
+    <x v="18"/>
+    <x v="6"/>
+    <n v="96600"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="50"/>
+    <x v="5"/>
+    <x v="3"/>
+    <n v="161000"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="19"/>
+    <x v="20"/>
+    <x v="21"/>
+    <n v="98300"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="51"/>
+    <x v="17"/>
+    <x v="20"/>
+    <n v="96800"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="52"/>
+    <x v="15"/>
+    <x v="23"/>
+    <n v="121100"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="44"/>
+    <x v="16"/>
+    <x v="5"/>
+    <n v="70700"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="44"/>
+    <x v="7"/>
+    <x v="21"/>
+    <n v="136800"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="53"/>
+    <x v="1"/>
+    <x v="24"/>
+    <n v="81300"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="20"/>
+    <x v="18"/>
+    <x v="10"/>
+    <n v="235200"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="54"/>
+    <x v="15"/>
+    <x v="0"/>
+    <n v="153200"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="55"/>
+    <x v="14"/>
+    <x v="6"/>
+    <n v="72100"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="56"/>
+    <x v="15"/>
+    <x v="1"/>
+    <n v="97900"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="57"/>
+    <x v="8"/>
+    <x v="16"/>
+    <n v="163400"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="58"/>
+    <x v="17"/>
+    <x v="25"/>
+    <n v="142800"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="29"/>
+    <x v="13"/>
+    <x v="10"/>
+    <n v="151300"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="59"/>
+    <x v="2"/>
+    <x v="18"/>
+    <n v="167400"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="15"/>
+    <x v="14"/>
+    <n v="77000"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="60"/>
+    <x v="11"/>
+    <x v="14"/>
+    <n v="129600"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="13"/>
+    <x v="13"/>
+    <x v="4"/>
+    <n v="92700"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="61"/>
+    <x v="3"/>
+    <x v="5"/>
+    <n v="169900"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="55"/>
+    <x v="16"/>
+    <x v="3"/>
+    <n v="104700"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="45"/>
+    <x v="7"/>
+    <x v="24"/>
+    <n v="121700"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="62"/>
+    <x v="8"/>
+    <x v="16"/>
+    <n v="109400"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="25"/>
+    <x v="0"/>
+    <x v="25"/>
+    <n v="101200"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="39"/>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="111100"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="63"/>
+    <x v="6"/>
+    <x v="0"/>
+    <n v="159100"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="60"/>
+    <x v="20"/>
+    <x v="0"/>
+    <n v="145500"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="60"/>
+    <x v="1"/>
+    <x v="12"/>
+    <n v="184500"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="64"/>
+    <x v="12"/>
+    <x v="25"/>
+    <n v="112600"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="46"/>
+    <x v="11"/>
+    <x v="17"/>
+    <n v="76700"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="65"/>
+    <x v="1"/>
+    <x v="14"/>
+    <n v="163900"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="66"/>
+    <x v="9"/>
+    <x v="18"/>
+    <n v="168900"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="67"/>
+    <x v="21"/>
+    <x v="5"/>
+    <n v="133300"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="34"/>
+    <x v="13"/>
+    <x v="3"/>
+    <n v="131100"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="57"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="118200"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="68"/>
+    <x v="2"/>
+    <x v="8"/>
+    <n v="146800"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="8"/>
+    <x v="10"/>
+    <x v="7"/>
+    <n v="126200"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="68"/>
+    <x v="11"/>
+    <x v="6"/>
+    <n v="117800"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="59"/>
+    <x v="12"/>
+    <x v="0"/>
+    <n v="89600"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="7">
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="1"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="70">
+        <item x="7"/>
+        <item x="55"/>
+        <item x="14"/>
+        <item x="23"/>
+        <item x="35"/>
+        <item x="12"/>
+        <item x="40"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="44"/>
+        <item x="51"/>
+        <item x="34"/>
+        <item x="33"/>
+        <item x="19"/>
+        <item x="54"/>
+        <item x="37"/>
+        <item x="9"/>
+        <item x="43"/>
+        <item x="4"/>
+        <item x="61"/>
+        <item x="27"/>
+        <item x="2"/>
+        <item x="24"/>
+        <item x="53"/>
+        <item x="18"/>
+        <item x="52"/>
+        <item x="58"/>
+        <item x="11"/>
+        <item x="31"/>
+        <item x="3"/>
+        <item x="38"/>
+        <item x="16"/>
+        <item x="42"/>
+        <item x="29"/>
+        <item x="62"/>
+        <item x="47"/>
+        <item x="25"/>
+        <item x="1"/>
+        <item x="50"/>
+        <item x="67"/>
+        <item x="15"/>
+        <item x="5"/>
+        <item x="63"/>
+        <item x="8"/>
+        <item x="46"/>
+        <item x="59"/>
+        <item x="48"/>
+        <item x="17"/>
+        <item x="66"/>
+        <item x="39"/>
+        <item x="32"/>
+        <item x="0"/>
+        <item x="49"/>
+        <item x="36"/>
+        <item x="56"/>
+        <item x="65"/>
+        <item x="57"/>
+        <item x="68"/>
+        <item x="26"/>
+        <item x="21"/>
+        <item x="30"/>
+        <item x="22"/>
+        <item x="64"/>
+        <item x="13"/>
+        <item x="41"/>
+        <item x="45"/>
+        <item x="60"/>
+        <item x="28"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="23">
+        <item x="4"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item x="16"/>
+        <item x="21"/>
+        <item x="13"/>
+        <item x="10"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="20"/>
+        <item x="17"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="18"/>
+        <item x="15"/>
+        <item x="19"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="27">
+        <item x="13"/>
+        <item x="14"/>
+        <item x="2"/>
+        <item x="11"/>
+        <item x="24"/>
+        <item x="22"/>
+        <item x="19"/>
+        <item x="17"/>
+        <item x="23"/>
+        <item x="4"/>
+        <item x="25"/>
+        <item x="9"/>
+        <item x="12"/>
+        <item x="20"/>
+        <item x="8"/>
+        <item x="16"/>
+        <item x="15"/>
+        <item x="21"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="18"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -429,269 +1842,323 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G101"/>
+  <dimension ref="A3:C20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="6"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="9"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="9"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="9"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="9"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="9"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="9"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="9"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="9"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="9"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="9"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="9"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="9"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="9"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="9"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="9"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:G105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17.6640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="E2" s="2">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="G2" s="2">
-        <v>119300</v>
+      <c r="A2" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="2">
-        <v>6.9</v>
-      </c>
-      <c r="E3" s="2">
-        <v>13</v>
-      </c>
-      <c r="F3" s="2">
-        <v>4.3</v>
-      </c>
-      <c r="G3" s="2">
-        <v>212200</v>
+      <c r="A3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2">
-        <v>3.9</v>
-      </c>
-      <c r="E4" s="2">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2">
-        <v>2.7</v>
-      </c>
-      <c r="G4" s="2">
-        <v>139400</v>
-      </c>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2">
-        <v>5.3</v>
-      </c>
-      <c r="E5" s="2">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="2">
-        <v>2.7</v>
-      </c>
-      <c r="G5" s="2">
-        <v>137200</v>
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2">
-        <v>3.4</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="E6" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F6" s="2">
-        <v>5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="G6" s="2">
-        <v>90100</v>
+        <v>119300</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="E7" s="2">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F7" s="2">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="G7" s="2">
-        <v>93100</v>
+        <v>212200</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" s="2">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="E8" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="G8" s="2">
-        <v>65600</v>
+        <v>139400</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="E9" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F9" s="2">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="G9" s="2">
-        <v>162400</v>
+        <v>137200</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="2">
-        <v>7.7</v>
+        <v>3.4</v>
       </c>
       <c r="E10" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F10" s="2">
-        <v>4.9000000000000004</v>
+        <v>5</v>
       </c>
       <c r="G10" s="2">
-        <v>118500</v>
+        <v>90100</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D11" s="2">
-        <v>2.7</v>
+        <v>7.5</v>
       </c>
       <c r="E11" s="2">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="G11" s="2">
-        <v>152800</v>
+        <v>93100</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -702,88 +2169,88 @@
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D12" s="2">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="E12" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F12" s="2">
-        <v>4.4000000000000004</v>
+        <v>3.4</v>
       </c>
       <c r="G12" s="2">
-        <v>71300</v>
+        <v>65600</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" s="2">
-        <v>5.0999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="E13" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F13" s="2">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="G13" s="2">
-        <v>212200</v>
+        <v>162400</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" s="2">
-        <v>1.1000000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="E14" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F14" s="2">
-        <v>2.7</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="G14" s="2">
-        <v>146000</v>
+        <v>118500</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D15" s="2">
-        <v>10.7</v>
+        <v>2.7</v>
       </c>
       <c r="E15" s="2">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="F15" s="2">
-        <v>4.4000000000000004</v>
+        <v>5</v>
       </c>
       <c r="G15" s="2">
-        <v>100400</v>
+        <v>152800</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -791,183 +2258,183 @@
         <v>9</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D16" s="2">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="E16" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F16" s="2">
-        <v>3.9</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="G16" s="2">
-        <v>76900</v>
+        <v>71300</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E17" s="2">
         <v>9</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="2">
-        <v>7.2</v>
-      </c>
-      <c r="E17" s="2">
-        <v>10</v>
-      </c>
       <c r="F17" s="2">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G17" s="2">
-        <v>98500</v>
+        <v>212200</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D18" s="2">
-        <v>5.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E18" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F18" s="2">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="G18" s="2">
-        <v>106300</v>
+        <v>146000</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D19" s="2">
-        <v>8.1999999999999993</v>
+        <v>10.7</v>
       </c>
       <c r="E19" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F19" s="2">
-        <v>2.8</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="G19" s="2">
-        <v>115100</v>
+        <v>100400</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D20" s="2">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="E20" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F20" s="2">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="G20" s="2">
-        <v>117100</v>
+        <v>76900</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D21" s="2">
-        <v>2.2999999999999998</v>
+        <v>7.2</v>
       </c>
       <c r="E21" s="2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F21" s="2">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="G21" s="2">
-        <v>107000</v>
+        <v>98500</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D22" s="2">
-        <v>11.8</v>
+        <v>5.5</v>
       </c>
       <c r="E22" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F22" s="2">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="G22" s="2">
-        <v>151000</v>
+        <v>106300</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D23" s="2">
-        <v>10.1</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="E23" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F23" s="2">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G23" s="2">
-        <v>113800</v>
+        <v>115100</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -975,22 +2442,22 @@
         <v>3</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D24" s="2">
-        <v>10.4</v>
+        <v>4.3</v>
       </c>
       <c r="E24" s="2">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F24" s="2">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="G24" s="2">
-        <v>110600</v>
+        <v>117100</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -998,211 +2465,211 @@
         <v>3</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D25" s="2">
-        <v>3.4</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E25" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F25" s="2">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="G25" s="2">
-        <v>111000</v>
+        <v>107000</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D26" s="2">
-        <v>0.9</v>
+        <v>11.8</v>
       </c>
       <c r="E26" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>4.0999999999999996</v>
+        <v>3.7</v>
       </c>
       <c r="G26" s="2">
-        <v>94700</v>
+        <v>151000</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D27" s="2">
-        <v>4</v>
+        <v>10.1</v>
       </c>
       <c r="E27" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F27" s="2">
-        <v>4.4000000000000004</v>
+        <v>2.6</v>
       </c>
       <c r="G27" s="2">
-        <v>131000</v>
+        <v>113800</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D28" s="2">
-        <v>6.7</v>
+        <v>10.4</v>
       </c>
       <c r="E28" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F28" s="2">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="G28" s="2">
-        <v>93200</v>
+        <v>110600</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D29" s="2">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="E29" s="2">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F29" s="2">
-        <v>4.9000000000000004</v>
+        <v>2.8</v>
       </c>
       <c r="G29" s="2">
-        <v>139200</v>
+        <v>111000</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D30" s="2">
-        <v>10</v>
+        <v>0.9</v>
       </c>
       <c r="E30" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F30" s="2">
-        <v>3.4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G30" s="2">
-        <v>122800</v>
+        <v>94700</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D31" s="2">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="E31" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F31" s="2">
-        <v>3.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="G31" s="2">
-        <v>95100</v>
+        <v>131000</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D32" s="2">
-        <v>11.6</v>
+        <v>6.7</v>
       </c>
       <c r="E32" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F32" s="2">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="G32" s="2">
-        <v>142400</v>
+        <v>93200</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D33" s="2">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="E33" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F33" s="2">
-        <v>3.1</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="G33" s="2">
-        <v>92900</v>
+        <v>139200</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>4</v>
@@ -1211,228 +2678,228 @@
         <v>17</v>
       </c>
       <c r="D34" s="2">
-        <v>10.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="E34" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F34" s="2">
-        <v>4.9000000000000004</v>
+        <v>3.4</v>
       </c>
       <c r="G34" s="2">
-        <v>87800</v>
+        <v>122800</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D35" s="2">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="E35" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F35" s="2">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="G35" s="2">
-        <v>157800</v>
+        <v>95100</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D36" s="2">
-        <v>5.2</v>
+        <v>11.6</v>
       </c>
       <c r="E36" s="2">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F36" s="2">
-        <v>4.9000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="G36" s="2">
-        <v>218200</v>
+        <v>142400</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D37" s="2">
-        <v>8.5</v>
+        <v>5.8</v>
       </c>
       <c r="E37" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F37" s="2">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G37" s="2">
-        <v>134100</v>
+        <v>92900</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D38" s="2">
-        <v>2.1</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="E38" s="2">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F38" s="2">
-        <v>4.7</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="G38" s="2">
-        <v>101600</v>
+        <v>87800</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="E39" s="2">
         <v>19</v>
       </c>
-      <c r="D39" s="2">
-        <v>2</v>
-      </c>
-      <c r="E39" s="2">
-        <v>6</v>
-      </c>
       <c r="F39" s="2">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="G39" s="2">
-        <v>71400</v>
+        <v>157800</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="2">
-        <v>11.6</v>
+        <v>5.2</v>
       </c>
       <c r="E40" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F40" s="2">
-        <v>5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="G40" s="2">
-        <v>134700</v>
+        <v>218200</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="2">
-        <v>8.6999999999999993</v>
+        <v>8.5</v>
       </c>
       <c r="E41" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F41" s="2">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G41" s="2">
-        <v>115300</v>
+        <v>134100</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D42" s="2">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="E42" s="2">
         <v>24</v>
       </c>
       <c r="F42" s="2">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="G42" s="2">
-        <v>94100</v>
+        <v>101600</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D43" s="2">
-        <v>5.0999999999999996</v>
+        <v>2</v>
       </c>
       <c r="E43" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F43" s="2">
-        <v>4.9000000000000004</v>
+        <v>3.8</v>
       </c>
       <c r="G43" s="2">
-        <v>99400</v>
+        <v>71400</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>4</v>
@@ -1441,476 +2908,476 @@
         <v>19</v>
       </c>
       <c r="D44" s="2">
-        <v>5.5</v>
+        <v>11.6</v>
       </c>
       <c r="E44" s="2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F44" s="2">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="G44" s="2">
-        <v>78100</v>
+        <v>134700</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D45" s="2">
-        <v>9.1</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="E45" s="2">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F45" s="2">
-        <v>4.0999999999999996</v>
+        <v>2.7</v>
       </c>
       <c r="G45" s="2">
-        <v>168900</v>
+        <v>115300</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D46" s="2">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="E46" s="2">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F46" s="2">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="G46" s="2">
-        <v>93400</v>
+        <v>94100</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D47" s="2">
-        <v>2.6</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="E47" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>3.6</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="G47" s="2">
-        <v>115100</v>
+        <v>99400</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D48" s="2">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="E48" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F48" s="2">
-        <v>4.0999999999999996</v>
+        <v>3.8</v>
       </c>
       <c r="G48" s="2">
-        <v>109800</v>
+        <v>78100</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D49" s="2">
-        <v>5.4</v>
+        <v>9.1</v>
       </c>
       <c r="E49" s="2">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F49" s="2">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G49" s="2">
-        <v>126400</v>
+        <v>168900</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D50" s="2">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="E50" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F50" s="2">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="G50" s="2">
-        <v>138200</v>
+        <v>93400</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D51" s="2">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="E51" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F51" s="2">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="G51" s="2">
-        <v>81700</v>
+        <v>115100</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="E52" s="2">
         <v>18</v>
       </c>
-      <c r="D52" s="2">
-        <v>11</v>
-      </c>
-      <c r="E52" s="2">
-        <v>14</v>
-      </c>
       <c r="F52" s="2">
-        <v>3.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G52" s="2">
-        <v>239300</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D53" s="2">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="E53" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F53" s="2">
-        <v>4.9000000000000004</v>
+        <v>4</v>
       </c>
       <c r="G53" s="2">
-        <v>149700</v>
+        <v>126400</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D54" s="2">
-        <v>3.3</v>
+        <v>8.4</v>
       </c>
       <c r="E54" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F54" s="2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G54" s="2">
-        <v>171800</v>
+        <v>138200</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D55" s="2">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="E55" s="2">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F55" s="2">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="G55" s="2">
-        <v>155300</v>
+        <v>81700</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D56" s="2">
-        <v>2.6</v>
+        <v>11</v>
       </c>
       <c r="E56" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>4.0999999999999996</v>
+        <v>3.2</v>
       </c>
       <c r="G56" s="2">
-        <v>126300</v>
+        <v>239300</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D57" s="2">
-        <v>11.2</v>
+        <v>5.6</v>
       </c>
       <c r="E57" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F57" s="2">
-        <v>3.2</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="G57" s="2">
-        <v>182800</v>
+        <v>149700</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D58" s="2">
-        <v>7.8</v>
+        <v>3.3</v>
       </c>
       <c r="E58" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F58" s="2">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="G58" s="2">
-        <v>93300</v>
+        <v>171800</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D59" s="2">
-        <v>6.4</v>
+        <v>1.6</v>
       </c>
       <c r="E59" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F59" s="2">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G59" s="2">
-        <v>98000</v>
+        <v>155300</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D60" s="2">
-        <v>8.1</v>
+        <v>2.6</v>
       </c>
       <c r="E60" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F60" s="2">
-        <v>3.4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G60" s="2">
-        <v>93100</v>
+        <v>126300</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D61" s="2">
-        <v>5.5</v>
+        <v>11.2</v>
       </c>
       <c r="E61" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F61" s="2">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G61" s="2">
-        <v>119200</v>
+        <v>182800</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="E62" s="2">
+        <v>20</v>
+      </c>
+      <c r="F62" s="2">
         <v>3</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D62" s="2">
-        <v>8.9</v>
-      </c>
-      <c r="E62" s="2">
-        <v>15</v>
-      </c>
-      <c r="F62" s="2">
-        <v>2.7</v>
-      </c>
       <c r="G62" s="2">
-        <v>119900</v>
+        <v>93300</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D63" s="2">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="E63" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F63" s="2">
-        <v>4.9000000000000004</v>
+        <v>3.7</v>
       </c>
       <c r="G63" s="2">
-        <v>96600</v>
+        <v>98000</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D64" s="2">
-        <v>7</v>
+        <v>8.1</v>
       </c>
       <c r="E64" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F64" s="2">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="G64" s="2">
-        <v>161000</v>
+        <v>93100</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
@@ -1921,19 +3388,19 @@
         <v>6</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D65" s="2">
-        <v>2.2999999999999998</v>
+        <v>5.5</v>
       </c>
       <c r="E65" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F65" s="2">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G65" s="2">
-        <v>98300</v>
+        <v>119200</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -1944,24 +3411,24 @@
         <v>4</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D66" s="2">
-        <v>1.9</v>
+        <v>8.9</v>
       </c>
       <c r="E66" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F66" s="2">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="G66" s="2">
-        <v>96800</v>
+        <v>119900</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>6</v>
@@ -1970,154 +3437,154 @@
         <v>19</v>
       </c>
       <c r="D67" s="2">
-        <v>4.4000000000000004</v>
+        <v>1</v>
       </c>
       <c r="E67" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F67" s="2">
-        <v>3.3</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="G67" s="2">
-        <v>121100</v>
+        <v>96600</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D68" s="2">
-        <v>1.6</v>
+        <v>7</v>
       </c>
       <c r="E68" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F68" s="2">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G68" s="2">
-        <v>70700</v>
+        <v>161000</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E69" s="2">
         <v>16</v>
-      </c>
-      <c r="D69" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="E69" s="2">
-        <v>4</v>
       </c>
       <c r="F69" s="2">
         <v>4.2</v>
       </c>
       <c r="G69" s="2">
-        <v>136800</v>
+        <v>98300</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D70" s="2">
-        <v>4.0999999999999996</v>
+        <v>1.9</v>
       </c>
       <c r="E70" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F70" s="2">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="G70" s="2">
-        <v>81300</v>
+        <v>96800</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D71" s="2">
-        <v>11.8</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="E71" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F71" s="2">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="G71" s="2">
-        <v>235200</v>
+        <v>121100</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="E72" s="2">
         <v>6</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D72" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="E72" s="2">
-        <v>22</v>
-      </c>
       <c r="F72" s="2">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="G72" s="2">
-        <v>153200</v>
+        <v>70700</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D73" s="2">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="E73" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F73" s="2">
-        <v>4.9000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="G73" s="2">
-        <v>72100</v>
+        <v>136800</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
@@ -2125,45 +3592,45 @@
         <v>9</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D74" s="2">
-        <v>9.3000000000000007</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="E74" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F74" s="2">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="G74" s="2">
-        <v>97900</v>
+        <v>81300</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D75" s="2">
-        <v>9.8000000000000007</v>
+        <v>11.8</v>
       </c>
       <c r="E75" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F75" s="2">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="G75" s="2">
-        <v>163400</v>
+        <v>235200</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
@@ -2174,180 +3641,180 @@
         <v>6</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D76" s="2">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="E76" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F76" s="2">
-        <v>3.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="G76" s="2">
-        <v>142800</v>
+        <v>153200</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D77" s="2">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="E77" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F77" s="2">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="G77" s="2">
-        <v>151300</v>
+        <v>72100</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D78" s="2">
-        <v>8</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="E78" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F78" s="2">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="G78" s="2">
-        <v>167400</v>
+        <v>97900</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D79" s="2">
-        <v>1.1000000000000001</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="E79" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F79" s="2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="G79" s="2">
-        <v>77000</v>
+        <v>163400</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D80" s="2">
-        <v>11.4</v>
+        <v>4.5</v>
       </c>
       <c r="E80" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F80" s="2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="G80" s="2">
-        <v>129600</v>
+        <v>142800</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D81" s="2">
-        <v>10.7</v>
+        <v>5.8</v>
       </c>
       <c r="E81" s="2">
         <v>8</v>
       </c>
       <c r="F81" s="2">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="G81" s="2">
-        <v>92700</v>
+        <v>151300</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D82" s="2">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="E82" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G82" s="2">
-        <v>169900</v>
+        <v>167400</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D83" s="2">
-        <v>0.7</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E83" s="2">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F83" s="2">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="G83" s="2">
-        <v>104700</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -2358,19 +3825,19 @@
         <v>10</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D84" s="2">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="E84" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F84" s="2">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="G84" s="2">
-        <v>121700</v>
+        <v>129600</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -2378,137 +3845,137 @@
         <v>9</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D85" s="2">
-        <v>6.3</v>
+        <v>10.7</v>
       </c>
       <c r="E85" s="2">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F85" s="2">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="G85" s="2">
-        <v>109400</v>
+        <v>92700</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D86" s="2">
-        <v>6.7</v>
+        <v>3.5</v>
       </c>
       <c r="E86" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F86" s="2">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G86" s="2">
-        <v>101200</v>
+        <v>169900</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="E87" s="2">
         <v>6</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D87" s="2">
-        <v>8.4</v>
-      </c>
-      <c r="E87" s="2">
-        <v>12</v>
-      </c>
       <c r="F87" s="2">
-        <v>4.9000000000000004</v>
+        <v>5</v>
       </c>
       <c r="G87" s="2">
-        <v>111100</v>
+        <v>104700</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D88" s="2">
-        <v>7.6</v>
+        <v>11.2</v>
       </c>
       <c r="E88" s="2">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F88" s="2">
-        <v>4.5999999999999996</v>
+        <v>2.9</v>
       </c>
       <c r="G88" s="2">
-        <v>159100</v>
+        <v>121700</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D89" s="2">
-        <v>11.4</v>
+        <v>6.3</v>
       </c>
       <c r="E89" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F89" s="2">
-        <v>4.5999999999999996</v>
+        <v>4</v>
       </c>
       <c r="G89" s="2">
-        <v>145500</v>
+        <v>109400</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D90" s="2">
-        <v>11.4</v>
+        <v>6.7</v>
       </c>
       <c r="E90" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F90" s="2">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="G90" s="2">
-        <v>184500</v>
+        <v>101200</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -2516,255 +3983,350 @@
         <v>3</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D91" s="2">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="E91" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F91" s="2">
-        <v>3.5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="G91" s="2">
-        <v>112600</v>
+        <v>111100</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C92" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D92" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="E92" s="2">
         <v>19</v>
       </c>
-      <c r="D92" s="2">
-        <v>7.8</v>
-      </c>
-      <c r="E92" s="2">
-        <v>11</v>
-      </c>
       <c r="F92" s="2">
-        <v>3.2</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="G92" s="2">
-        <v>76700</v>
+        <v>159100</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D93" s="2">
-        <v>9.6999999999999993</v>
+        <v>11.4</v>
       </c>
       <c r="E93" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F93" s="2">
-        <v>2.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="G93" s="2">
-        <v>163900</v>
+        <v>145500</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D94" s="2">
-        <v>8.3000000000000007</v>
+        <v>11.4</v>
       </c>
       <c r="E94" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F94" s="2">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="G94" s="2">
-        <v>168900</v>
+        <v>184500</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D95" s="2">
-        <v>7.1</v>
+        <v>10.5</v>
       </c>
       <c r="E95" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F95" s="2">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="G95" s="2">
-        <v>133300</v>
+        <v>112600</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D96" s="2">
-        <v>2</v>
+        <v>7.8</v>
       </c>
       <c r="E96" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F96" s="2">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="G96" s="2">
-        <v>131100</v>
+        <v>76700</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D97" s="2">
-        <v>9.8000000000000007</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="E97" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F97" s="2">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="G97" s="2">
-        <v>118200</v>
+        <v>163900</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C98" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" s="2">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E98" s="2">
         <v>18</v>
       </c>
-      <c r="D98" s="2">
-        <v>9.9</v>
-      </c>
-      <c r="E98" s="2">
-        <v>14</v>
-      </c>
       <c r="F98" s="2">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="G98" s="2">
-        <v>146800</v>
+        <v>168900</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D99" s="2">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="E99" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F99" s="2">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="G99" s="2">
-        <v>126200</v>
+        <v>133300</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D100" s="2">
-        <v>9.9</v>
+        <v>2</v>
       </c>
       <c r="E100" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F100" s="2">
-        <v>4.9000000000000004</v>
+        <v>5</v>
       </c>
       <c r="G100" s="2">
-        <v>117800</v>
+        <v>131100</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D101" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="E101" s="2">
+        <v>15</v>
+      </c>
+      <c r="F101" s="2">
+        <v>5</v>
+      </c>
+      <c r="G101" s="2">
+        <v>118200</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D102" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="E102" s="2">
+        <v>14</v>
+      </c>
+      <c r="F102" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="G102" s="2">
+        <v>146800</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D103" s="2">
+        <v>7.7</v>
+      </c>
+      <c r="E103" s="2">
         <v>9</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="F103" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G103" s="2">
+        <v>126200</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D104" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="E104" s="2">
+        <v>11</v>
+      </c>
+      <c r="F104" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G104" s="2">
+        <v>117800</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C105" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D105" s="2">
         <v>8</v>
       </c>
-      <c r="E101" s="2">
+      <c r="E105" s="2">
         <v>10</v>
       </c>
-      <c r="F101" s="2">
+      <c r="F105" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="G101" s="2">
+      <c r="G105" s="2">
         <v>89600</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>